--- a/analysis/raw/tariffs/section_338.xlsx
+++ b/analysis/raw/tariffs/section_338.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coding\SoC\tariffs\tariffs\analysis\raw\tariffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5794120D-CAA4-4C42-8065-ED02F3BA0BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB77127A-19BC-4607-8287-970E1B2DC57E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{BA941A06-664E-493C-8C92-0761EF42121C}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{BA941A06-664E-493C-8C92-0761EF42121C}"/>
   </bookViews>
   <sheets>
-    <sheet name="alcohol" sheetId="1" r:id="rId1"/>
+    <sheet name="alcohol aug 22" sheetId="1" r:id="rId1"/>
     <sheet name="alcohol sep 29" sheetId="4" r:id="rId2"/>
     <sheet name="alcohol sep 29 excl" sheetId="5" r:id="rId3"/>
-    <sheet name="dairy" sheetId="2" r:id="rId4"/>
+    <sheet name="dairy aug 22" sheetId="2" r:id="rId4"/>
     <sheet name="dairy sep 29 excl" sheetId="6" r:id="rId5"/>
-    <sheet name="motor" sheetId="3" r:id="rId6"/>
+    <sheet name="motor aug 22" sheetId="3" r:id="rId6"/>
     <sheet name="motor sep 29" sheetId="7" r:id="rId7"/>
     <sheet name="motor sep 29 excl" sheetId="8" r:id="rId8"/>
   </sheets>
